--- a/Testing_Data/2026_06_Festo/EncoderCalibration.xlsx
+++ b/Testing_Data/2026_06_Festo/EncoderCalibration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Bipedal_Robot\Testing_Data\2026_06_Festo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB17C26-3667-467A-9EFE-7E3F6CAD7F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8C77EEA-9D2D-42F3-BEBF-F56EB8777BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11910" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{ED23B71C-6DC7-4F03-A302-FE33CB0246DD}"/>
   </bookViews>
@@ -276,108 +276,78 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$21</c:f>
+              <c:f>Sheet1!$A$2:$A$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>602</c:v>
+                  <c:v>906</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>844</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>723</c:v>
+                  <c:v>433</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>491</c:v>
+                  <c:v>886</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>598</c:v>
+                  <c:v>843</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>531</c:v>
+                  <c:v>742</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>524</c:v>
+                  <c:v>671</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>732</c:v>
+                  <c:v>638</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>848</c:v>
+                  <c:v>608</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>893</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>906</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>778</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>708</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>664</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>568</c:v>
+                  <c:v>575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$21</c:f>
+              <c:f>Sheet1!$B$2:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-109</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-103</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>-90</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>-45</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>21</c:v>
+                  <c:v>-50</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>27</c:v>
+                  <c:v>-25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-45</c:v>
+                  <c:v>-13</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-90</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-110</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-114</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-64</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-40</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-24</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>10.5</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1139,12 +1109,12 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>201930</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>74295</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>506730</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>131445</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1470,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07EB23B-8D5C-452B-917B-439C5A6B7860}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -1487,204 +1457,152 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>602</v>
+        <v>906</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>-109</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>844</v>
+        <v>375</v>
       </c>
       <c r="B3">
-        <v>-90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>723</v>
+        <v>433</v>
       </c>
       <c r="B4">
-        <v>-45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>491</v>
+        <v>886</v>
       </c>
       <c r="B5">
-        <v>37</v>
+        <v>-103</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>598</v>
+        <v>843</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>531</v>
+        <v>742</v>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>524</v>
+        <v>671</v>
       </c>
       <c r="B8">
-        <v>27</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>732</v>
+        <v>638</v>
       </c>
       <c r="B9">
-        <v>-45</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>848</v>
+        <v>608</v>
       </c>
       <c r="B10">
-        <v>-90</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>893</v>
+        <v>575</v>
       </c>
       <c r="B11">
-        <v>-110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>906</v>
-      </c>
-      <c r="B12">
-        <v>-114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>778</v>
-      </c>
-      <c r="B13">
-        <v>-64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>708</v>
-      </c>
-      <c r="B14">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>664</v>
-      </c>
-      <c r="B15">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>568</v>
-      </c>
-      <c r="B16">
-        <v>10.5</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>543</v>
+      </c>
+      <c r="C23">
+        <f>-0.359*B23+215.25</f>
+        <v>20.313000000000017</v>
+      </c>
+      <c r="D23">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>707</v>
+      </c>
+      <c r="C24">
+        <f t="shared" ref="C24:C28" si="0">-0.359*B24+215.25</f>
+        <v>-38.562999999999988</v>
+      </c>
+      <c r="D24">
+        <v>-37</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>215.25</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>215.25</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>215.25</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B29">
-        <v>747</v>
-      </c>
-      <c r="C29">
-        <f>-0.3629*B29+216.74</f>
-        <v>-54.346299999999985</v>
-      </c>
-      <c r="D29">
-        <v>-51</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B30">
-        <v>747</v>
-      </c>
-      <c r="C30">
-        <f t="shared" ref="C30:C34" si="0">-0.3629*B30+216.74</f>
-        <v>-54.346299999999985</v>
-      </c>
-      <c r="D30">
-        <v>-51</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B31">
-        <v>896</v>
-      </c>
-      <c r="C31">
+      <c r="C28">
         <f t="shared" si="0"/>
-        <v>-108.41840000000002</v>
-      </c>
-      <c r="D31">
-        <v>-109</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B32">
-        <v>510</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="0"/>
-        <v>31.661000000000001</v>
-      </c>
-      <c r="D32">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33">
-        <f t="shared" si="0"/>
-        <v>216.74</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C34">
-        <f t="shared" si="0"/>
-        <v>216.74</v>
+        <v>215.25</v>
       </c>
     </row>
   </sheetData>
